--- a/Team_Performance_Tracker.xlsx
+++ b/Team_Performance_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/pdinh4_cougarnet_uh_edu/Documents/Documents/GitHub/MIS3371-Section10129-Group8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414AD234-1A15-49E6-B0CD-7B3F99DDDE09}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB18108B-196C-4C69-A758-85DB6CC6FDFB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DE0A00-6593-4680-85C6-5158FC367019}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Team Member</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Sep 20-Group Exercise Pack</t>
+  </si>
+  <si>
+    <t>Sep 21-23: Presentation Layer</t>
   </si>
 </sst>
 </file>
@@ -126,8 +129,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -143,6 +146,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216E1F5F-0E78-468B-83D6-E608256C5D4A}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -472,32 +479,36 @@
     <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -519,8 +530,11 @@
       <c r="G2">
         <v>100</v>
       </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -542,8 +556,11 @@
       <c r="G3">
         <v>100</v>
       </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -565,8 +582,11 @@
       <c r="G4">
         <v>100</v>
       </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -588,8 +608,11 @@
       <c r="G5">
         <v>100</v>
       </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -609,6 +632,9 @@
         <v>100</v>
       </c>
       <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
         <v>100</v>
       </c>
     </row>

--- a/Team_Performance_Tracker.xlsx
+++ b/Team_Performance_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/pdinh4_cougarnet_uh_edu/Documents/Documents/GitHub/MIS3371-Section10129-Group8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB18108B-196C-4C69-A758-85DB6CC6FDFB}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDF5B4EF-B235-4EC6-8AC0-453931ED64B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DE0A00-6593-4680-85C6-5158FC367019}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Team Member</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>Sep 21-23: Presentation Layer</t>
+  </si>
+  <si>
+    <t>Sep 28th-30</t>
+  </si>
+  <si>
+    <t>Oct 5-7</t>
   </si>
 </sst>
 </file>
@@ -129,8 +135,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216E1F5F-0E78-468B-83D6-E608256C5D4A}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -482,7 +488,7 @@
     <col min="8" max="8" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,8 +513,14 @@
       <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -533,8 +545,14 @@
       <c r="H2">
         <v>100</v>
       </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -559,8 +577,14 @@
       <c r="H3">
         <v>100</v>
       </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -585,8 +609,14 @@
       <c r="H4">
         <v>100</v>
       </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -611,8 +641,14 @@
       <c r="H5">
         <v>100</v>
       </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -635,6 +671,12 @@
         <v>100</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>100</v>
       </c>
     </row>

--- a/Team_Performance_Tracker.xlsx
+++ b/Team_Performance_Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/pdinh4_cougarnet_uh_edu/Documents/Documents/GitHub/MIS3371-Section10129-Group8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1769e2fa3f00123/Documents/GitHub/MIS3371-Section10129-Group8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDF5B4EF-B235-4EC6-8AC0-453931ED64B3}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40599E14-2259-4E15-9980-8473A9C2FA1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DE0A00-6593-4680-85C6-5158FC367019}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Team Member</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Oct 5-7</t>
+  </si>
+  <si>
+    <t>Oct 12-14: Milestone 2 + Group Activity</t>
   </si>
 </sst>
 </file>
@@ -152,10 +155,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216E1F5F-0E78-468B-83D6-E608256C5D4A}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -488,7 +487,7 @@
     <col min="8" max="8" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,8 +518,11 @@
       <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -551,8 +553,11 @@
       <c r="J2">
         <v>100</v>
       </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -583,8 +588,11 @@
       <c r="J3">
         <v>100</v>
       </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -615,8 +623,11 @@
       <c r="J4">
         <v>100</v>
       </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -647,8 +658,11 @@
       <c r="J5">
         <v>100</v>
       </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -677,6 +691,9 @@
         <v>100</v>
       </c>
       <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>100</v>
       </c>
     </row>

--- a/Team_Performance_Tracker.xlsx
+++ b/Team_Performance_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e1769e2fa3f00123/Documents/GitHub/MIS3371-Section10129-Group8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40599E14-2259-4E15-9980-8473A9C2FA1A}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{BA7B3E8B-FC56-4D36-80C9-15D7C099C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D877F621-078F-462B-A3D7-4453044C72B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DE0A00-6593-4680-85C6-5158FC367019}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Team Member</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Oct 12-14: Milestone 2 + Group Activity</t>
+  </si>
+  <si>
+    <t>Sep 19th-21st</t>
   </si>
 </sst>
 </file>
@@ -155,6 +158,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216E1F5F-0E78-468B-83D6-E608256C5D4A}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -487,7 +494,7 @@
     <col min="8" max="8" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,8 +528,11 @@
       <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -556,8 +566,11 @@
       <c r="K2">
         <v>100</v>
       </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -591,8 +604,11 @@
       <c r="K3">
         <v>100</v>
       </c>
+      <c r="L3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -626,8 +642,11 @@
       <c r="K4">
         <v>100</v>
       </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -661,8 +680,11 @@
       <c r="K5">
         <v>100</v>
       </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -694,6 +716,9 @@
         <v>100</v>
       </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>100</v>
       </c>
     </row>
